--- a/Structure_Data/text.9.14/20260915_04/structure_factor_20260915_04.xlsx
+++ b/Structure_Data/text.9.14/20260915_04/structure_factor_20260915_04.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D364"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3819 @@
         <v>16.3093166023735</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.418251037597656</v>
+      </c>
+      <c r="C30">
+        <v>0.416736602783203</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.418251037597656</v>
+      </c>
+      <c r="C31">
+        <v>0.416736602783203</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.214168548583984</v>
+      </c>
+      <c r="C32">
+        <v>0.0138092041015625</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.0201072692871094</v>
+      </c>
+      <c r="C33">
+        <v>0.000736236572265625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.00588226318359375</v>
+      </c>
+      <c r="C34">
+        <v>0.0001983642578125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.00244522094726562</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.00030517578125</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.5</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>43955</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1.24720737117507</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>0.988200718414604</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.05</v>
+      </c>
+      <c r="B53">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.1</v>
+      </c>
+      <c r="B54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.15</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.2</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.25</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.3</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.35</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.4</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.45</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.5</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.55</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.6</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.65</v>
+      </c>
+      <c r="B65">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.7</v>
+      </c>
+      <c r="B66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.75</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.8</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.85</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.9</v>
+      </c>
+      <c r="B70">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.95</v>
+      </c>
+      <c r="B71">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.5</v>
+      </c>
+      <c r="B73">
+        <v>17941</v>
+      </c>
+      <c r="C73">
+        <v>0.408167443976794</v>
+      </c>
+      <c r="D73">
+        <v>0.408167443976794</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74">
+        <v>10493</v>
+      </c>
+      <c r="C74">
+        <v>0.238721419633716</v>
+      </c>
+      <c r="D74">
+        <v>0.646888863610511</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>1.5</v>
+      </c>
+      <c r="B75">
+        <v>6124</v>
+      </c>
+      <c r="C75">
+        <v>0.139324308952338</v>
+      </c>
+      <c r="D75">
+        <v>0.786213172562848</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>2</v>
+      </c>
+      <c r="B76">
+        <v>3687</v>
+      </c>
+      <c r="C76">
+        <v>0.0838812421795018</v>
+      </c>
+      <c r="D76">
+        <v>0.87009441474235</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>2.5</v>
+      </c>
+      <c r="B77">
+        <v>2243</v>
+      </c>
+      <c r="C77">
+        <v>0.0510294619497213</v>
+      </c>
+      <c r="D77">
+        <v>0.921123876692071</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78">
+        <v>1325</v>
+      </c>
+      <c r="C78">
+        <v>0.0301444659310659</v>
+      </c>
+      <c r="D78">
+        <v>0.951268342623137</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>3.5</v>
+      </c>
+      <c r="B79">
+        <v>844</v>
+      </c>
+      <c r="C79">
+        <v>0.0192014560345808</v>
+      </c>
+      <c r="D79">
+        <v>0.970469798657718</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>4</v>
+      </c>
+      <c r="B80">
+        <v>484</v>
+      </c>
+      <c r="C80">
+        <v>0.011011261517461</v>
+      </c>
+      <c r="D80">
+        <v>0.981481060175179</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>4.5</v>
+      </c>
+      <c r="B81">
+        <v>310</v>
+      </c>
+      <c r="C81">
+        <v>0.00705266750085314</v>
+      </c>
+      <c r="D81">
+        <v>0.988533727676032</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>5</v>
+      </c>
+      <c r="B82">
+        <v>184</v>
+      </c>
+      <c r="C82">
+        <v>0.00418609941986122</v>
+      </c>
+      <c r="D82">
+        <v>0.992719827095894</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>5.5</v>
+      </c>
+      <c r="B83">
+        <v>120</v>
+      </c>
+      <c r="C83">
+        <v>0.00273006483903993</v>
+      </c>
+      <c r="D83">
+        <v>0.995449891934933</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>6</v>
+      </c>
+      <c r="B84">
+        <v>71</v>
+      </c>
+      <c r="C84">
+        <v>0.00161528836309862</v>
+      </c>
+      <c r="D84">
+        <v>0.997065180298032</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>6.5</v>
+      </c>
+      <c r="B85">
+        <v>50</v>
+      </c>
+      <c r="C85">
+        <v>0.00113752701626664</v>
+      </c>
+      <c r="D85">
+        <v>0.998202707314299</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>7</v>
+      </c>
+      <c r="B86">
+        <v>36</v>
+      </c>
+      <c r="C86">
+        <v>0.000819019451711978</v>
+      </c>
+      <c r="D86">
+        <v>0.999021726766011</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>7.5</v>
+      </c>
+      <c r="B87">
+        <v>22</v>
+      </c>
+      <c r="C87">
+        <v>0.00050051188715732</v>
+      </c>
+      <c r="D87">
+        <v>0.999522238653168</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>8</v>
+      </c>
+      <c r="B88">
+        <v>8</v>
+      </c>
+      <c r="C88">
+        <v>0.000182004322602662</v>
+      </c>
+      <c r="D88">
+        <v>0.999704242975771</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>8.5</v>
+      </c>
+      <c r="B89">
+        <v>5</v>
+      </c>
+      <c r="C89">
+        <v>0.000113752701626664</v>
+      </c>
+      <c r="D89">
+        <v>0.999817995677397</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>9</v>
+      </c>
+      <c r="B90">
+        <v>4</v>
+      </c>
+      <c r="C90">
+        <v>9.10021613013309e-05</v>
+      </c>
+      <c r="D90">
+        <v>0.999908997838699</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>9.5</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>2.27505403253327e-05</v>
+      </c>
+      <c r="D91">
+        <v>0.999931748379024</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>10</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92">
+        <v>6.82516209759982e-05</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>152502</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>0.727534527588628</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>0.496125708279799</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>0.05</v>
+      </c>
+      <c r="B107">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>0.1</v>
+      </c>
+      <c r="B108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>0.15</v>
+      </c>
+      <c r="B109">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>0.2</v>
+      </c>
+      <c r="B110">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>0.25</v>
+      </c>
+      <c r="B111">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>0.3</v>
+      </c>
+      <c r="B112">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>0.35</v>
+      </c>
+      <c r="B113">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0.4</v>
+      </c>
+      <c r="B114">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>0.45</v>
+      </c>
+      <c r="B115">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>0.5</v>
+      </c>
+      <c r="B116">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0.55</v>
+      </c>
+      <c r="B117">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.6</v>
+      </c>
+      <c r="B118">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.65</v>
+      </c>
+      <c r="B119">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.7</v>
+      </c>
+      <c r="B120">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.75</v>
+      </c>
+      <c r="B121">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.8</v>
+      </c>
+      <c r="B122">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.85</v>
+      </c>
+      <c r="B123">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.9</v>
+      </c>
+      <c r="B124">
+        <v>1.4142135623731</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>0.95</v>
+      </c>
+      <c r="B125">
+        <v>1.87082869338697</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>0.5</v>
+      </c>
+      <c r="B127">
+        <v>105106</v>
+      </c>
+      <c r="C127">
+        <v>0.68921063330317</v>
+      </c>
+      <c r="D127">
+        <v>0.68921063330317</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B128">
+        <v>18265</v>
+      </c>
+      <c r="C128">
+        <v>0.11976892106333</v>
+      </c>
+      <c r="D128">
+        <v>0.8089795543665</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B129">
+        <v>3225</v>
+      </c>
+      <c r="C129">
+        <v>0.021147263642444</v>
+      </c>
+      <c r="D129">
+        <v>0.830126818008944</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>1</v>
+      </c>
+      <c r="B130">
+        <v>2301</v>
+      </c>
+      <c r="C130">
+        <v>0.0150883267104694</v>
+      </c>
+      <c r="D130">
+        <v>0.845215144719414</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B131">
+        <v>5171</v>
+      </c>
+      <c r="C131">
+        <v>0.0339077520294816</v>
+      </c>
+      <c r="D131">
+        <v>0.879122896748895</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B132">
+        <v>3026</v>
+      </c>
+      <c r="C132">
+        <v>0.0198423627231118</v>
+      </c>
+      <c r="D132">
+        <v>0.898965259472007</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B133">
+        <v>1285</v>
+      </c>
+      <c r="C133">
+        <v>0.00842611900171801</v>
+      </c>
+      <c r="D133">
+        <v>0.907391378473725</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>1.5</v>
+      </c>
+      <c r="B134">
+        <v>2563</v>
+      </c>
+      <c r="C134">
+        <v>0.0168063369660726</v>
+      </c>
+      <c r="D134">
+        <v>0.924197715439798</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B135">
+        <v>1441</v>
+      </c>
+      <c r="C135">
+        <v>0.00944905640581763</v>
+      </c>
+      <c r="D135">
+        <v>0.933646771845615</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B136">
+        <v>1097</v>
+      </c>
+      <c r="C136">
+        <v>0.00719334828395693</v>
+      </c>
+      <c r="D136">
+        <v>0.940840120129572</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B137">
+        <v>379</v>
+      </c>
+      <c r="C137">
+        <v>0.00248521330867792</v>
+      </c>
+      <c r="D137">
+        <v>0.94332533343825</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B138">
+        <v>904</v>
+      </c>
+      <c r="C138">
+        <v>0.00592779111093625</v>
+      </c>
+      <c r="D138">
+        <v>0.949253124549186</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B139">
+        <v>1366</v>
+      </c>
+      <c r="C139">
+        <v>0.00895725957692358</v>
+      </c>
+      <c r="D139">
+        <v>0.95821038412611</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>2</v>
+      </c>
+      <c r="B140">
+        <v>172</v>
+      </c>
+      <c r="C140">
+        <v>0.00112785406093035</v>
+      </c>
+      <c r="D140">
+        <v>0.95933823818704</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B141">
+        <v>1005</v>
+      </c>
+      <c r="C141">
+        <v>0.00659007750718023</v>
+      </c>
+      <c r="D141">
+        <v>0.96592831569422</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B142">
+        <v>551</v>
+      </c>
+      <c r="C142">
+        <v>0.00361306736960827</v>
+      </c>
+      <c r="D142">
+        <v>0.969541383063829</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B143">
+        <v>327</v>
+      </c>
+      <c r="C143">
+        <v>0.00214423417397805</v>
+      </c>
+      <c r="D143">
+        <v>0.971685617237807</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B144">
+        <v>305</v>
+      </c>
+      <c r="C144">
+        <v>0.00199997377083579</v>
+      </c>
+      <c r="D144">
+        <v>0.973685591008642</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B145">
+        <v>508</v>
+      </c>
+      <c r="C145">
+        <v>0.00333110385437568</v>
+      </c>
+      <c r="D145">
+        <v>0.977016694863018</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B146">
+        <v>225</v>
+      </c>
+      <c r="C146">
+        <v>0.00147539048668214</v>
+      </c>
+      <c r="D146">
+        <v>0.9784920853497</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B147">
+        <v>211</v>
+      </c>
+      <c r="C147">
+        <v>0.00138358841195525</v>
+      </c>
+      <c r="D147">
+        <v>0.979875673761656</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2.5</v>
+      </c>
+      <c r="B148">
+        <v>236</v>
+      </c>
+      <c r="C148">
+        <v>0.00154752068825327</v>
+      </c>
+      <c r="D148">
+        <v>0.981423194449909</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B149">
+        <v>472</v>
+      </c>
+      <c r="C149">
+        <v>0.00309504137650654</v>
+      </c>
+      <c r="D149">
+        <v>0.984518235826415</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B150">
+        <v>164</v>
+      </c>
+      <c r="C150">
+        <v>0.00107539573251498</v>
+      </c>
+      <c r="D150">
+        <v>0.98559363155893</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B151">
+        <v>342</v>
+      </c>
+      <c r="C151">
+        <v>0.00224259353975686</v>
+      </c>
+      <c r="D151">
+        <v>0.987836225098687</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B152">
+        <v>167</v>
+      </c>
+      <c r="C152">
+        <v>0.00109506760567075</v>
+      </c>
+      <c r="D152">
+        <v>0.988931292704358</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B153">
+        <v>52</v>
+      </c>
+      <c r="C153">
+        <v>0.000340979134699873</v>
+      </c>
+      <c r="D153">
+        <v>0.989272271839058</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B154">
+        <v>171</v>
+      </c>
+      <c r="C154">
+        <v>0.00112129676987843</v>
+      </c>
+      <c r="D154">
+        <v>0.990393568608936</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B155">
+        <v>154</v>
+      </c>
+      <c r="C155">
+        <v>0.00100982282199578</v>
+      </c>
+      <c r="D155">
+        <v>0.991403391430932</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B156">
+        <v>123</v>
+      </c>
+      <c r="C156">
+        <v>0.000806546799386238</v>
+      </c>
+      <c r="D156">
+        <v>0.992209938230318</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>3</v>
+      </c>
+      <c r="B157">
+        <v>67</v>
+      </c>
+      <c r="C157">
+        <v>0.000439338500478682</v>
+      </c>
+      <c r="D157">
+        <v>0.992649276730797</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B158">
+        <v>54</v>
+      </c>
+      <c r="C158">
+        <v>0.000354093716803714</v>
+      </c>
+      <c r="D158">
+        <v>0.993003370447601</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B159">
+        <v>136</v>
+      </c>
+      <c r="C159">
+        <v>0.000891791583061206</v>
+      </c>
+      <c r="D159">
+        <v>0.993895162030662</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B160">
+        <v>46</v>
+      </c>
+      <c r="C160">
+        <v>0.000301635388388349</v>
+      </c>
+      <c r="D160">
+        <v>0.99419679741905</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B161">
+        <v>163</v>
+      </c>
+      <c r="C161">
+        <v>0.00106883844146306</v>
+      </c>
+      <c r="D161">
+        <v>0.995265635860513</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B162">
+        <v>68</v>
+      </c>
+      <c r="C162">
+        <v>0.000445895791530603</v>
+      </c>
+      <c r="D162">
+        <v>0.995711531652044</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B163">
+        <v>26</v>
+      </c>
+      <c r="C163">
+        <v>0.000170489567349936</v>
+      </c>
+      <c r="D163">
+        <v>0.995882021219394</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B164">
+        <v>24</v>
+      </c>
+      <c r="C164">
+        <v>0.000157374985246095</v>
+      </c>
+      <c r="D164">
+        <v>0.99603939620464</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B165">
+        <v>73</v>
+      </c>
+      <c r="C165">
+        <v>0.000478682246790206</v>
+      </c>
+      <c r="D165">
+        <v>0.99651807845143</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B166">
+        <v>43</v>
+      </c>
+      <c r="C166">
+        <v>0.000281963515232587</v>
+      </c>
+      <c r="D166">
+        <v>0.996800041966663</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B167">
+        <v>8</v>
+      </c>
+      <c r="C167">
+        <v>5.2458328415365e-05</v>
+      </c>
+      <c r="D167">
+        <v>0.996852500295078</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>3.5</v>
+      </c>
+      <c r="B168">
+        <v>44</v>
+      </c>
+      <c r="C168">
+        <v>0.000288520806284508</v>
+      </c>
+      <c r="D168">
+        <v>0.997141021101363</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B169">
+        <v>64</v>
+      </c>
+      <c r="C169">
+        <v>0.00041966662732292</v>
+      </c>
+      <c r="D169">
+        <v>0.997560687728686</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B170">
+        <v>45</v>
+      </c>
+      <c r="C170">
+        <v>0.000295078097336428</v>
+      </c>
+      <c r="D170">
+        <v>0.997855765826022</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B171">
+        <v>18</v>
+      </c>
+      <c r="C171">
+        <v>0.000118031238934571</v>
+      </c>
+      <c r="D171">
+        <v>0.997973797064956</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B172">
+        <v>48</v>
+      </c>
+      <c r="C172">
+        <v>0.00031474997049219</v>
+      </c>
+      <c r="D172">
+        <v>0.998288547035449</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B173">
+        <v>51</v>
+      </c>
+      <c r="C173">
+        <v>0.000334421843647952</v>
+      </c>
+      <c r="D173">
+        <v>0.998622968879097</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B174">
+        <v>16</v>
+      </c>
+      <c r="C174">
+        <v>0.00010491665683073</v>
+      </c>
+      <c r="D174">
+        <v>0.998727885535927</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B175">
+        <v>11</v>
+      </c>
+      <c r="C175">
+        <v>7.21302015711269e-05</v>
+      </c>
+      <c r="D175">
+        <v>0.998800015737499</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B176">
+        <v>12</v>
+      </c>
+      <c r="C176">
+        <v>7.86874926230476e-05</v>
+      </c>
+      <c r="D176">
+        <v>0.998878703230122</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B177">
+        <v>26</v>
+      </c>
+      <c r="C177">
+        <v>0.000170489567349936</v>
+      </c>
+      <c r="D177">
+        <v>0.999049192797472</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B178">
+        <v>18</v>
+      </c>
+      <c r="C178">
+        <v>0.000118031238934571</v>
+      </c>
+      <c r="D178">
+        <v>0.999167224036406</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B179">
+        <v>25</v>
+      </c>
+      <c r="C179">
+        <v>0.000163932276298016</v>
+      </c>
+      <c r="D179">
+        <v>0.999331156312704</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>4</v>
+      </c>
+      <c r="B180">
+        <v>3</v>
+      </c>
+      <c r="C180">
+        <v>1.96718731557619e-05</v>
+      </c>
+      <c r="D180">
+        <v>0.99935082818586</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B181">
+        <v>19</v>
+      </c>
+      <c r="C181">
+        <v>0.000124588529986492</v>
+      </c>
+      <c r="D181">
+        <v>0.999475416715846</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B182">
+        <v>22</v>
+      </c>
+      <c r="C182">
+        <v>0.000144260403142254</v>
+      </c>
+      <c r="D182">
+        <v>0.999619677118989</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>4.09267638593623</v>
+      </c>
+      <c r="B183">
+        <v>2</v>
+      </c>
+      <c r="C183">
+        <v>1.31145821038413e-05</v>
+      </c>
+      <c r="D183">
+        <v>0.999632791701092</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B184">
+        <v>9</v>
+      </c>
+      <c r="C184">
+        <v>5.90156194672857e-05</v>
+      </c>
+      <c r="D184">
+        <v>0.99969180732056</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B185">
+        <v>16</v>
+      </c>
+      <c r="C185">
+        <v>0.00010491665683073</v>
+      </c>
+      <c r="D185">
+        <v>0.999796723977391</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>4.24264068711928</v>
+      </c>
+      <c r="B186">
+        <v>6</v>
+      </c>
+      <c r="C186">
+        <v>3.93437463115238e-05</v>
+      </c>
+      <c r="D186">
+        <v>0.999836067723702</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>4.27200187265877</v>
+      </c>
+      <c r="B187">
+        <v>5</v>
+      </c>
+      <c r="C187">
+        <v>3.27864552596032e-05</v>
+      </c>
+      <c r="D187">
+        <v>0.999868854178962</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B188">
+        <v>11</v>
+      </c>
+      <c r="C188">
+        <v>7.21302015711269e-05</v>
+      </c>
+      <c r="D188">
+        <v>0.999940984380533</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>4.33012701892219</v>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+      <c r="C189">
+        <v>6.55729105192063e-06</v>
+      </c>
+      <c r="D189">
+        <v>0.999947541671585</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>4.38748219369606</v>
+      </c>
+      <c r="B190">
+        <v>2</v>
+      </c>
+      <c r="C190">
+        <v>1.31145821038413e-05</v>
+      </c>
+      <c r="D190">
+        <v>0.999960656253688</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>4.47213595499958</v>
+      </c>
+      <c r="B191">
+        <v>2</v>
+      </c>
+      <c r="C191">
+        <v>1.31145821038413e-05</v>
+      </c>
+      <c r="D191">
+        <v>0.999973770835792</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>4.5</v>
+      </c>
+      <c r="B192">
+        <v>2</v>
+      </c>
+      <c r="C192">
+        <v>1.31145821038413e-05</v>
+      </c>
+      <c r="D192">
+        <v>0.999986885417896</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>4.60977222864644</v>
+      </c>
+      <c r="B193">
+        <v>1</v>
+      </c>
+      <c r="C193">
+        <v>6.55729105192063e-06</v>
+      </c>
+      <c r="D193">
+        <v>0.999993442708948</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>4.7169905660283</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194">
+        <v>6.55729105192063e-06</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195"/>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.418251037597656</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>0</v>
+      </c>
+      <c r="B206">
+        <v>0.418251037597656</v>
+      </c>
+      <c r="C206">
+        <v>1</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>0.5</v>
+      </c>
+      <c r="B207">
+        <v>0.25201416015625</v>
+      </c>
+      <c r="C207">
+        <v>6</v>
+      </c>
+      <c r="D207">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>1</v>
+      </c>
+      <c r="B208">
+        <v>0.218105316162109</v>
+      </c>
+      <c r="C208">
+        <v>26</v>
+      </c>
+      <c r="D208">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>1.5</v>
+      </c>
+      <c r="B209">
+        <v>0.206583404541016</v>
+      </c>
+      <c r="C209">
+        <v>90</v>
+      </c>
+      <c r="D209">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>2</v>
+      </c>
+      <c r="B210">
+        <v>0.206534542254548</v>
+      </c>
+      <c r="C210">
+        <v>134</v>
+      </c>
+      <c r="D210">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>2.5</v>
+      </c>
+      <c r="B211">
+        <v>0.205184078955835</v>
+      </c>
+      <c r="C211">
+        <v>258</v>
+      </c>
+      <c r="D211">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>3</v>
+      </c>
+      <c r="B212">
+        <v>0.203573868914348</v>
+      </c>
+      <c r="C212">
+        <v>410</v>
+      </c>
+      <c r="D212">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>3.5</v>
+      </c>
+      <c r="B213">
+        <v>0.202055649236146</v>
+      </c>
+      <c r="C213">
+        <v>494</v>
+      </c>
+      <c r="D213">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>4</v>
+      </c>
+      <c r="B214">
+        <v>0.200631205240885</v>
+      </c>
+      <c r="C214">
+        <v>690</v>
+      </c>
+      <c r="D214">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>4.5</v>
+      </c>
+      <c r="B215">
+        <v>0.199153717738923</v>
+      </c>
+      <c r="C215">
+        <v>962</v>
+      </c>
+      <c r="D215">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>5</v>
+      </c>
+      <c r="B216">
+        <v>0.197758485276408</v>
+      </c>
+      <c r="C216">
+        <v>1098</v>
+      </c>
+      <c r="D216">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>5.5</v>
+      </c>
+      <c r="B217">
+        <v>0.196371770345978</v>
+      </c>
+      <c r="C217">
+        <v>1406</v>
+      </c>
+      <c r="D217">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>6</v>
+      </c>
+      <c r="B218">
+        <v>0.195005820580157</v>
+      </c>
+      <c r="C218">
+        <v>1578</v>
+      </c>
+      <c r="D218">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>6.5</v>
+      </c>
+      <c r="B219">
+        <v>0.193647443243959</v>
+      </c>
+      <c r="C219">
+        <v>2018</v>
+      </c>
+      <c r="D219">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>7</v>
+      </c>
+      <c r="B220">
+        <v>0.192302123997376</v>
+      </c>
+      <c r="C220">
+        <v>2342</v>
+      </c>
+      <c r="D220">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>7.5</v>
+      </c>
+      <c r="B221">
+        <v>0.190918944872231</v>
+      </c>
+      <c r="C221">
+        <v>2634</v>
+      </c>
+      <c r="D221">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>8</v>
+      </c>
+      <c r="B222">
+        <v>0.189571445712457</v>
+      </c>
+      <c r="C222">
+        <v>2930</v>
+      </c>
+      <c r="D222">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>8.5</v>
+      </c>
+      <c r="B223">
+        <v>0.18826084260307</v>
+      </c>
+      <c r="C223">
+        <v>3402</v>
+      </c>
+      <c r="D223">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>9</v>
+      </c>
+      <c r="B224">
+        <v>0.186993208820578</v>
+      </c>
+      <c r="C224">
+        <v>3926</v>
+      </c>
+      <c r="D224">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>9.5</v>
+      </c>
+      <c r="B225">
+        <v>0.185743563509412</v>
+      </c>
+      <c r="C225">
+        <v>4266</v>
+      </c>
+      <c r="D225">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>10</v>
+      </c>
+      <c r="B226">
+        <v>0.184521458567323</v>
+      </c>
+      <c r="C226">
+        <v>4730</v>
+      </c>
+      <c r="D226">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>10.5</v>
+      </c>
+      <c r="B227">
+        <v>0.183302957912106</v>
+      </c>
+      <c r="C227">
+        <v>5510</v>
+      </c>
+      <c r="D227">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>11</v>
+      </c>
+      <c r="B228">
+        <v>0.182171047612601</v>
+      </c>
+      <c r="C228">
+        <v>5562</v>
+      </c>
+      <c r="D228">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>11.5</v>
+      </c>
+      <c r="B229">
+        <v>0.181083737520643</v>
+      </c>
+      <c r="C229">
+        <v>6410</v>
+      </c>
+      <c r="D229">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>12</v>
+      </c>
+      <c r="B230">
+        <v>0.180056322682654</v>
+      </c>
+      <c r="C230">
+        <v>6894</v>
+      </c>
+      <c r="D230">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>12.5</v>
+      </c>
+      <c r="B231">
+        <v>0.17908705238984</v>
+      </c>
+      <c r="C231">
+        <v>7490</v>
+      </c>
+      <c r="D231">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>13</v>
+      </c>
+      <c r="B232">
+        <v>0.178147726874283</v>
+      </c>
+      <c r="C232">
+        <v>8258</v>
+      </c>
+      <c r="D232">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>13.5</v>
+      </c>
+      <c r="B233">
+        <v>0.177229308912376</v>
+      </c>
+      <c r="C233">
+        <v>8994</v>
+      </c>
+      <c r="D233">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>14</v>
+      </c>
+      <c r="B234">
+        <v>0.176365304947303</v>
+      </c>
+      <c r="C234">
+        <v>9446</v>
+      </c>
+      <c r="D234">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>14.5</v>
+      </c>
+      <c r="B235">
+        <v>0.175598045130439</v>
+      </c>
+      <c r="C235">
+        <v>9978</v>
+      </c>
+      <c r="D235">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>15</v>
+      </c>
+      <c r="B236">
+        <v>0.174857351419891</v>
+      </c>
+      <c r="C236">
+        <v>11138</v>
+      </c>
+      <c r="D236">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>15.5</v>
+      </c>
+      <c r="B237">
+        <v>0.174204429534158</v>
+      </c>
+      <c r="C237">
+        <v>11406</v>
+      </c>
+      <c r="D237">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>16</v>
+      </c>
+      <c r="B238">
+        <v>0.17354655271496</v>
+      </c>
+      <c r="C238">
+        <v>12575</v>
+      </c>
+      <c r="D238">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>16.5</v>
+      </c>
+      <c r="B239">
+        <v>0.172866848010946</v>
+      </c>
+      <c r="C239">
+        <v>12848</v>
+      </c>
+      <c r="D239">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>17</v>
+      </c>
+      <c r="B240">
+        <v>0.171953830118005</v>
+      </c>
+      <c r="C240">
+        <v>12060</v>
+      </c>
+      <c r="D240">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>17.5</v>
+      </c>
+      <c r="B241">
+        <v>0.171105743222057</v>
+      </c>
+      <c r="C241">
+        <v>11804</v>
+      </c>
+      <c r="D241">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>18</v>
+      </c>
+      <c r="B242">
+        <v>0.170308162270894</v>
+      </c>
+      <c r="C242">
+        <v>11016</v>
+      </c>
+      <c r="D242">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>18.5</v>
+      </c>
+      <c r="B243">
+        <v>0.169564163350613</v>
+      </c>
+      <c r="C243">
+        <v>10700</v>
+      </c>
+      <c r="D243">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>19</v>
+      </c>
+      <c r="B244">
+        <v>0.168879911321849</v>
+      </c>
+      <c r="C244">
+        <v>9756</v>
+      </c>
+      <c r="D244">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>19.5</v>
+      </c>
+      <c r="B245">
+        <v>0.168271606524716</v>
+      </c>
+      <c r="C245">
+        <v>9224</v>
+      </c>
+      <c r="D245">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>20</v>
+      </c>
+      <c r="B246">
+        <v>0.167679774885967</v>
+      </c>
+      <c r="C246">
+        <v>8408</v>
+      </c>
+      <c r="D246">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>20.5</v>
+      </c>
+      <c r="B247">
+        <v>0.167148239946596</v>
+      </c>
+      <c r="C247">
+        <v>7452</v>
+      </c>
+      <c r="D247">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>21</v>
+      </c>
+      <c r="B248">
+        <v>0.16668863621625</v>
+      </c>
+      <c r="C248">
+        <v>7040</v>
+      </c>
+      <c r="D248">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>21.5</v>
+      </c>
+      <c r="B249">
+        <v>0.166236106636598</v>
+      </c>
+      <c r="C249">
+        <v>5820</v>
+      </c>
+      <c r="D249">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>22</v>
+      </c>
+      <c r="B250">
+        <v>0.165905122287938</v>
+      </c>
+      <c r="C250">
+        <v>4880</v>
+      </c>
+      <c r="D250">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>22.5</v>
+      </c>
+      <c r="B251">
+        <v>0.165529960539283</v>
+      </c>
+      <c r="C251">
+        <v>3936</v>
+      </c>
+      <c r="D251">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>23</v>
+      </c>
+      <c r="B252">
+        <v>0.165059699261733</v>
+      </c>
+      <c r="C252">
+        <v>2999</v>
+      </c>
+      <c r="D252">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>23.5</v>
+      </c>
+      <c r="B253">
+        <v>0.164722820596957</v>
+      </c>
+      <c r="C253">
+        <v>2180</v>
+      </c>
+      <c r="D253">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>24</v>
+      </c>
+      <c r="B254">
+        <v>0.164413386215398</v>
+      </c>
+      <c r="C254">
+        <v>1620</v>
+      </c>
+      <c r="D254">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>24.5</v>
+      </c>
+      <c r="B255">
+        <v>0.164226948820203</v>
+      </c>
+      <c r="C255">
+        <v>1208</v>
+      </c>
+      <c r="D255">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>25</v>
+      </c>
+      <c r="B256">
+        <v>0.164146577223598</v>
+      </c>
+      <c r="C256">
+        <v>942</v>
+      </c>
+      <c r="D256">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>25.5</v>
+      </c>
+      <c r="B257">
+        <v>0.164113867772769</v>
+      </c>
+      <c r="C257">
+        <v>584</v>
+      </c>
+      <c r="D257">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>26</v>
+      </c>
+      <c r="B258">
+        <v>0.164103763204225</v>
+      </c>
+      <c r="C258">
+        <v>284</v>
+      </c>
+      <c r="D258">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>26.5</v>
+      </c>
+      <c r="B259">
+        <v>0.164055784543355</v>
+      </c>
+      <c r="C259">
+        <v>192</v>
+      </c>
+      <c r="D259">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>27</v>
+      </c>
+      <c r="B260">
+        <v>0.164159994858962</v>
+      </c>
+      <c r="C260">
+        <v>104</v>
+      </c>
+      <c r="D260">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>27.5</v>
+      </c>
+      <c r="B261">
+        <v>0.164008776346842</v>
+      </c>
+      <c r="C261">
+        <v>24</v>
+      </c>
+      <c r="D261">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>28</v>
+      </c>
+      <c r="B262">
+        <v>0.163467407226562</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+      <c r="D262">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>0</v>
+      </c>
+      <c r="B264">
+        <v>0.418251037597656</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>0.5</v>
+      </c>
+      <c r="B265">
+        <v>0.250576019287109</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>1</v>
+      </c>
+      <c r="B266">
+        <v>0.212841033935547</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>1.5</v>
+      </c>
+      <c r="B267">
+        <v>0.205165863037109</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>2</v>
+      </c>
+      <c r="B268">
+        <v>0.20538330078125</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>2.5</v>
+      </c>
+      <c r="B269">
+        <v>0.204227447509766</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>3</v>
+      </c>
+      <c r="B270">
+        <v>0.203109741210938</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>3.5</v>
+      </c>
+      <c r="B271">
+        <v>0.201465606689453</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>4</v>
+      </c>
+      <c r="B272">
+        <v>0.200416564941406</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>4.5</v>
+      </c>
+      <c r="B273">
+        <v>0.198287963867188</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>5</v>
+      </c>
+      <c r="B274">
+        <v>0.197910308837891</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>5.5</v>
+      </c>
+      <c r="B275">
+        <v>0.196727752685547</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>6</v>
+      </c>
+      <c r="B276">
+        <v>0.195369720458984</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>6.5</v>
+      </c>
+      <c r="B277">
+        <v>0.193538665771484</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>7</v>
+      </c>
+      <c r="B278">
+        <v>0.192020416259766</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>7.5</v>
+      </c>
+      <c r="B279">
+        <v>0.190788269042969</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>8</v>
+      </c>
+      <c r="B280">
+        <v>0.189064025878906</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>8.5</v>
+      </c>
+      <c r="B281">
+        <v>0.187412261962891</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>9</v>
+      </c>
+      <c r="B282">
+        <v>0.186565399169922</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>9.5</v>
+      </c>
+      <c r="B283">
+        <v>0.185173034667969</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>10</v>
+      </c>
+      <c r="B284">
+        <v>0.184196472167969</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>10.5</v>
+      </c>
+      <c r="B285">
+        <v>0.182373046875</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>11</v>
+      </c>
+      <c r="B286">
+        <v>0.181499481201172</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>11.5</v>
+      </c>
+      <c r="B287">
+        <v>0.179836273193359</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>12</v>
+      </c>
+      <c r="B288">
+        <v>0.17877197265625</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>12.5</v>
+      </c>
+      <c r="B289">
+        <v>0.177719116210938</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>13</v>
+      </c>
+      <c r="B290">
+        <v>0.177188873291016</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>13.5</v>
+      </c>
+      <c r="B291">
+        <v>0.177345275878906</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>14</v>
+      </c>
+      <c r="B292">
+        <v>0.176616668701172</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>14.5</v>
+      </c>
+      <c r="B293">
+        <v>0.175628662109375</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>15</v>
+      </c>
+      <c r="B294">
+        <v>0.174961090087891</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>15.5</v>
+      </c>
+      <c r="B295">
+        <v>0.176059722900391</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>16</v>
+      </c>
+      <c r="B296">
+        <v>0.17578125</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>0</v>
+      </c>
+      <c r="B298">
+        <v>0.418251037597656</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>0.5</v>
+      </c>
+      <c r="B299">
+        <v>0.248893737792969</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>1</v>
+      </c>
+      <c r="B300">
+        <v>0.213451385498047</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>1.5</v>
+      </c>
+      <c r="B301">
+        <v>0.205821990966797</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>2</v>
+      </c>
+      <c r="B302">
+        <v>0.206836700439453</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>2.5</v>
+      </c>
+      <c r="B303">
+        <v>0.204967498779297</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>3</v>
+      </c>
+      <c r="B304">
+        <v>0.204139709472656</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>3.5</v>
+      </c>
+      <c r="B305">
+        <v>0.202369689941406</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>4</v>
+      </c>
+      <c r="B306">
+        <v>0.201202392578125</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>4.5</v>
+      </c>
+      <c r="B307">
+        <v>0.199726104736328</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>5</v>
+      </c>
+      <c r="B308">
+        <v>0.199203491210938</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>5.5</v>
+      </c>
+      <c r="B309">
+        <v>0.197475433349609</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>6</v>
+      </c>
+      <c r="B310">
+        <v>0.196430206298828</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>6.5</v>
+      </c>
+      <c r="B311">
+        <v>0.195087432861328</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>7</v>
+      </c>
+      <c r="B312">
+        <v>0.194061279296875</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>7.5</v>
+      </c>
+      <c r="B313">
+        <v>0.192569732666016</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>8</v>
+      </c>
+      <c r="B314">
+        <v>0.192268371582031</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>8.5</v>
+      </c>
+      <c r="B315">
+        <v>0.191349029541016</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>9</v>
+      </c>
+      <c r="B316">
+        <v>0.189849853515625</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>9.5</v>
+      </c>
+      <c r="B317">
+        <v>0.188587188720703</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>10</v>
+      </c>
+      <c r="B318">
+        <v>0.18841552734375</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>10.5</v>
+      </c>
+      <c r="B319">
+        <v>0.187240600585938</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>11</v>
+      </c>
+      <c r="B320">
+        <v>0.186054229736328</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>11.5</v>
+      </c>
+      <c r="B321">
+        <v>0.185447692871094</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>12</v>
+      </c>
+      <c r="B322">
+        <v>0.184970855712891</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>12.5</v>
+      </c>
+      <c r="B323">
+        <v>0.185249328613281</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>13</v>
+      </c>
+      <c r="B324">
+        <v>0.184455871582031</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>13.5</v>
+      </c>
+      <c r="B325">
+        <v>0.183616638183594</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>14</v>
+      </c>
+      <c r="B326">
+        <v>0.184127807617188</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>14.5</v>
+      </c>
+      <c r="B327">
+        <v>0.184288024902344</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>15</v>
+      </c>
+      <c r="B328">
+        <v>0.183555603027344</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>15.5</v>
+      </c>
+      <c r="B329">
+        <v>0.183574676513672</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>16</v>
+      </c>
+      <c r="B330">
+        <v>0.183074951171875</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>0</v>
+      </c>
+      <c r="B332">
+        <v>0.418251037597656</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>0.5</v>
+      </c>
+      <c r="B333">
+        <v>0.256572723388672</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>1</v>
+      </c>
+      <c r="B334">
+        <v>0.212753295898438</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>1.5</v>
+      </c>
+      <c r="B335">
+        <v>0.204872131347656</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>2</v>
+      </c>
+      <c r="B336">
+        <v>0.205524444580078</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>2.5</v>
+      </c>
+      <c r="B337">
+        <v>0.202800750732422</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>3</v>
+      </c>
+      <c r="B338">
+        <v>0.201881408691406</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>3.5</v>
+      </c>
+      <c r="B339">
+        <v>0.201007843017578</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>4</v>
+      </c>
+      <c r="B340">
+        <v>0.199989318847656</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>4.5</v>
+      </c>
+      <c r="B341">
+        <v>0.197544097900391</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>5</v>
+      </c>
+      <c r="B342">
+        <v>0.196247100830078</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>5.5</v>
+      </c>
+      <c r="B343">
+        <v>0.194950103759766</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>6</v>
+      </c>
+      <c r="B344">
+        <v>0.193557739257812</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>6.5</v>
+      </c>
+      <c r="B345">
+        <v>0.192638397216797</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>7</v>
+      </c>
+      <c r="B346">
+        <v>0.191581726074219</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>7.5</v>
+      </c>
+      <c r="B347">
+        <v>0.189693450927734</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>8</v>
+      </c>
+      <c r="B348">
+        <v>0.188541412353516</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>8.5</v>
+      </c>
+      <c r="B349">
+        <v>0.186393737792969</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>9</v>
+      </c>
+      <c r="B350">
+        <v>0.185169219970703</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>9.5</v>
+      </c>
+      <c r="B351">
+        <v>0.184268951416016</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>10</v>
+      </c>
+      <c r="B352">
+        <v>0.1829833984375</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>10.5</v>
+      </c>
+      <c r="B353">
+        <v>0.182216644287109</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>11</v>
+      </c>
+      <c r="B354">
+        <v>0.180995941162109</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>11.5</v>
+      </c>
+      <c r="B355">
+        <v>0.179996490478516</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>12</v>
+      </c>
+      <c r="B356">
+        <v>0.179069519042969</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>12.5</v>
+      </c>
+      <c r="B357">
+        <v>0.177085876464844</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>13</v>
+      </c>
+      <c r="B358">
+        <v>0.176120758056641</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>13.5</v>
+      </c>
+      <c r="B359">
+        <v>0.175075531005859</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>14</v>
+      </c>
+      <c r="B360">
+        <v>0.174983978271484</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>14.5</v>
+      </c>
+      <c r="B361">
+        <v>0.174800872802734</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>15</v>
+      </c>
+      <c r="B362">
+        <v>0.174163818359375</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>15.5</v>
+      </c>
+      <c r="B363">
+        <v>0.173503875732422</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>16</v>
+      </c>
+      <c r="B364">
+        <v>0.173721313476562</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>